--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>136365608</v>
       </c>
       <c r="B34" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136361547</v>
       </c>
       <c r="B77" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136362814</v>
       </c>
       <c r="B78" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136362816</v>
       </c>
       <c r="B252" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>136362819</v>
       </c>
       <c r="B253" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>136361228</v>
       </c>
       <c r="B259" t="n">
-        <v>93428</v>
+        <v>93431</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>136365608</v>
       </c>
       <c r="B34" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136361547</v>
       </c>
       <c r="B77" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136362814</v>
       </c>
       <c r="B78" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136362816</v>
       </c>
       <c r="B252" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>136362819</v>
       </c>
       <c r="B253" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>136361228</v>
       </c>
       <c r="B259" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>136365609</v>
       </c>
       <c r="B11" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>136365608</v>
       </c>
       <c r="B34" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136361547</v>
       </c>
       <c r="B77" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136362814</v>
       </c>
       <c r="B78" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>136362809</v>
       </c>
       <c r="B102" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>136362811</v>
       </c>
       <c r="B103" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>136362813</v>
       </c>
       <c r="B104" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>136362817</v>
       </c>
       <c r="B105" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>136362818</v>
       </c>
       <c r="B106" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>136361231</v>
       </c>
       <c r="B108" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>136361225</v>
       </c>
       <c r="B119" t="n">
-        <v>79560</v>
+        <v>79562</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>136361226</v>
       </c>
       <c r="B180" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>136361289</v>
       </c>
       <c r="B181" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>136362820</v>
       </c>
       <c r="B182" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>136365610</v>
       </c>
       <c r="B183" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>136365611</v>
       </c>
       <c r="B184" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136361230</v>
       </c>
       <c r="B191" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>136361548</v>
       </c>
       <c r="B210" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>136361229</v>
       </c>
       <c r="B214" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>136361288</v>
       </c>
       <c r="B215" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>136362810</v>
       </c>
       <c r="B216" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>136362815</v>
       </c>
       <c r="B217" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>135890374</v>
       </c>
       <c r="B218" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136362816</v>
       </c>
       <c r="B252" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>136362819</v>
       </c>
       <c r="B253" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>136361228</v>
       </c>
       <c r="B259" t="n">
-        <v>93432</v>
+        <v>93437</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>136362808</v>
       </c>
       <c r="B265" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>136365607</v>
       </c>
       <c r="B266" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -4119,7 +4119,7 @@
         <v>136365608</v>
       </c>
       <c r="B34" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136361547</v>
       </c>
       <c r="B77" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136362814</v>
       </c>
       <c r="B78" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136362816</v>
       </c>
       <c r="B252" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>136362819</v>
       </c>
       <c r="B253" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>136361228</v>
       </c>
       <c r="B259" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>136365609</v>
       </c>
       <c r="B11" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>136365608</v>
       </c>
       <c r="B34" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136361547</v>
       </c>
       <c r="B77" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136362814</v>
       </c>
       <c r="B78" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>136362809</v>
       </c>
       <c r="B102" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>136362811</v>
       </c>
       <c r="B103" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>136362813</v>
       </c>
       <c r="B104" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>136362817</v>
       </c>
       <c r="B105" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>136362818</v>
       </c>
       <c r="B106" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>136361231</v>
       </c>
       <c r="B108" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>136361225</v>
       </c>
       <c r="B119" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>136361226</v>
       </c>
       <c r="B180" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>136361289</v>
       </c>
       <c r="B181" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>136362820</v>
       </c>
       <c r="B182" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>136365610</v>
       </c>
       <c r="B183" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>136365611</v>
       </c>
       <c r="B184" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136361230</v>
       </c>
       <c r="B191" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136362816</v>
       </c>
       <c r="B252" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>136362819</v>
       </c>
       <c r="B253" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>136361228</v>
       </c>
       <c r="B259" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>136362808</v>
       </c>
       <c r="B265" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>136365607</v>
       </c>
       <c r="B266" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>136365609</v>
       </c>
       <c r="B11" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>136365608</v>
       </c>
       <c r="B34" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136361547</v>
       </c>
       <c r="B77" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136362814</v>
       </c>
       <c r="B78" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>136362809</v>
       </c>
       <c r="B102" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>136362811</v>
       </c>
       <c r="B103" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>136362813</v>
       </c>
       <c r="B104" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>136362817</v>
       </c>
       <c r="B105" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>136362818</v>
       </c>
       <c r="B106" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>136361231</v>
       </c>
       <c r="B108" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>136361225</v>
       </c>
       <c r="B119" t="n">
-        <v>79566</v>
+        <v>79568</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>136361226</v>
       </c>
       <c r="B180" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>136361289</v>
       </c>
       <c r="B181" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>136362820</v>
       </c>
       <c r="B182" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>136365610</v>
       </c>
       <c r="B183" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>136365611</v>
       </c>
       <c r="B184" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136361230</v>
       </c>
       <c r="B191" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136362816</v>
       </c>
       <c r="B252" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>136362819</v>
       </c>
       <c r="B253" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>136361228</v>
       </c>
       <c r="B259" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>136362808</v>
       </c>
       <c r="B265" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>136365607</v>
       </c>
       <c r="B266" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -23793,7 +23793,7 @@
         <v>135890374</v>
       </c>
       <c r="B218" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -23793,7 +23793,7 @@
         <v>135890374</v>
       </c>
       <c r="B218" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
